--- a/examples/localized/zh_TW/sample.xlsx
+++ b/examples/localized/zh_TW/sample.xlsx
@@ -631,7 +631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -650,6 +650,11 @@
           <t>顏色</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>文字模式</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -667,6 +672,11 @@
           <t>#e5b5a5</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>adv</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -682,6 +692,11 @@
       <c r="C3" t="inlineStr">
         <is>
           <t>#b0c9ed</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>adv</t>
         </is>
       </c>
     </row>
